--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -138,18 +138,18 @@
     <t>Desc Desc Desc</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -168,109 +168,109 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>ILLESCAS</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PEDRO ANGEL</t>
   </si>
   <si>
+    <t>JOSE RUBEN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN ALFONSO</t>
+  </si>
+  <si>
     <t>MILKA SARAY</t>
   </si>
   <si>
+    <t>REDA ALAN</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
+    <t>DAVID</t>
+  </si>
+  <si>
     <t>RONALDO</t>
   </si>
   <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>ILLESCAS</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>REDA ALAN</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -774,7 +774,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -828,7 +828,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1005,7 +1005,7 @@
         <v>6</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1059,7 +1059,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1313,7 +1313,7 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1367,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1467,7 +1467,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1521,7 +1521,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1698,7 +1698,7 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1752,7 +1752,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2021,7 +2021,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>90</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2257,7 +2257,7 @@
         <v>95</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>95</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
@@ -2861,30 +2861,30 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>64.29000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
@@ -2905,7 +2905,7 @@
         <v>28.57</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
@@ -2925,19 +2925,19 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>71.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G5">
-        <v>28.57</v>
+        <v>14.29</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
@@ -2957,19 +2957,19 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3017,7 +3017,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3042,106 +3042,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920135</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920140</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920145</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920147</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920382</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3183,92 +3083,92 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920138</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920145</v>
+        <v>21330051920139</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920147</v>
+        <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920382</v>
+        <v>21330051650295</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920138</v>
+        <v>21330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
         <v>76</v>
@@ -3279,13 +3179,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920139</v>
+        <v>21330051920143</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>77</v>
@@ -3296,13 +3196,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051650295</v>
+        <v>21330051920145</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>78</v>
@@ -3313,13 +3213,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920141</v>
+        <v>21330051920146</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>79</v>
@@ -3330,13 +3230,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920143</v>
+        <v>21330051920147</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>80</v>
@@ -3347,13 +3247,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920146</v>
+        <v>21330051920148</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>81</v>
@@ -3364,13 +3264,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920148</v>
+        <v>21330051920150</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
         <v>82</v>
@@ -3381,13 +3281,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920150</v>
+        <v>21330051920382</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
         <v>83</v>
@@ -3401,10 +3301,10 @@
         <v>21330051920392</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
         <v>84</v>
@@ -3420,7 +3320,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3455,13 +3355,13 @@
         <v>21330051920141</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3478,19 +3378,19 @@
         <v>21330051920141</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3498,47 +3398,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920148</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920148</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -135,7 +135,7 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Muñoz Rivadeneyra Salvador</t>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="59">
   <si>
     <t>Materia</t>
   </si>
@@ -141,12 +140,12 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -165,121 +164,46 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>ILLESCAS</t>
-  </si>
-  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>REDA ALAN</t>
-  </si>
-  <si>
     <t>ALBERTO SHAKIB</t>
   </si>
   <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
     <t>RONALDO</t>
   </si>
   <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
     <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -332,11 +256,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -777,10 +702,10 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -789,7 +714,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -813,7 +738,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -854,10 +779,10 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -866,7 +791,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -893,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -902,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -931,10 +856,10 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -943,7 +868,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -967,10 +892,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -979,7 +904,7 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1008,10 +933,10 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1020,7 +945,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1047,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1085,10 +1010,10 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1097,7 +1022,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1133,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1162,10 +1087,10 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1174,7 +1099,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1198,7 +1123,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1239,10 +1164,10 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1251,7 +1176,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1275,7 +1200,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1287,7 +1212,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1316,10 +1241,10 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1328,7 +1253,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1352,10 +1277,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1393,10 +1318,10 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1405,7 +1330,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1470,10 +1395,10 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1482,7 +1407,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1509,7 +1434,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1518,7 +1443,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1547,10 +1472,10 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1559,7 +1484,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1583,7 +1508,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1595,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1624,10 +1549,10 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1636,7 +1561,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1660,7 +1585,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1672,7 +1597,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1701,10 +1626,10 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1713,7 +1638,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1737,10 +1662,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1778,10 +1703,10 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1790,7 +1715,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1817,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1965,10 +1890,10 @@
         <v>86.7</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1977,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2024,10 +1949,10 @@
         <v>120</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2036,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -2083,10 +2008,10 @@
         <v>113.3</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2095,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2142,10 +2067,10 @@
         <v>113.3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2154,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -2201,10 +2126,10 @@
         <v>113.3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2213,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -2260,10 +2185,10 @@
         <v>113.3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2272,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2319,10 +2244,10 @@
         <v>113.3</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2331,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -2378,10 +2303,10 @@
         <v>93.3</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2390,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -2437,10 +2362,10 @@
         <v>120</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2449,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -2496,10 +2421,10 @@
         <v>80</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2508,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -2555,10 +2480,10 @@
         <v>113.3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2567,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -2614,10 +2539,10 @@
         <v>106.7</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2626,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -2673,10 +2598,10 @@
         <v>66.7</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2685,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -2732,10 +2657,10 @@
         <v>120</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2744,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -2784,6 +2709,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2834,11 +2761,11 @@
       <c r="E2">
         <v>6</v>
       </c>
-      <c r="F2">
-        <v>57.14</v>
-      </c>
-      <c r="G2">
-        <v>42.86</v>
+      <c r="F2" s="2">
+        <v>57.1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>42.9</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -2846,7 +2773,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2866,11 +2793,11 @@
       <c r="E3">
         <v>4</v>
       </c>
-      <c r="F3">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="G3">
-        <v>28.57</v>
+      <c r="F3" s="2">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>28.6</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -2878,13 +2805,13 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
@@ -2893,30 +2820,30 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="G4">
-        <v>28.57</v>
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>85.7</v>
+      </c>
+      <c r="G4" s="2">
+        <v>14.3</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
@@ -2925,24 +2852,24 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="G5">
-        <v>14.29</v>
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7.1</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2962,10 +2889,10 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
@@ -2974,7 +2901,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2994,19 +2921,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3051,276 +2978,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920135</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920138</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920139</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920140</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051650295</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920141</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920143</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920145</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920146</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920147</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920148</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920150</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920382</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920392</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3355,13 +3013,13 @@
         <v>21330051920141</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3378,19 +3036,19 @@
         <v>21330051920141</v>
       </c>
       <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3398,24 +3056,116 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
+        <v>21330051920147</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920147</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920382</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920382</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
         <v>21330051920148</v>
       </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="G4">
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="56">
   <si>
     <t>Materia</t>
   </si>
@@ -164,37 +164,28 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
   </si>
 </sst>
 </file>
@@ -708,10 +699,10 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -785,10 +776,10 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -862,10 +853,10 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -898,10 +889,10 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -939,10 +930,10 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -975,10 +966,10 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1016,10 +1007,10 @@
         <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1093,10 +1084,10 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1129,10 +1120,10 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1170,10 +1161,10 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>8</v>
@@ -1247,10 +1238,10 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -1324,10 +1315,10 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>8</v>
@@ -1401,10 +1392,10 @@
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1478,10 +1469,10 @@
         <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1517,7 +1508,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1555,10 +1546,10 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1594,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1632,10 +1623,10 @@
         <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1709,10 +1700,10 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -1745,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1896,10 +1887,10 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L4">
         <v>90</v>
@@ -1955,10 +1946,10 @@
         <v>96.7</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -2014,10 +2005,10 @@
         <v>96.7</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -2073,10 +2064,10 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L7">
         <v>85</v>
@@ -2132,10 +2123,10 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -2191,10 +2182,10 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L9">
         <v>95</v>
@@ -2250,10 +2241,10 @@
         <v>96.7</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -2309,10 +2300,10 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L11">
         <v>90</v>
@@ -2368,10 +2359,10 @@
         <v>96.7</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -2427,10 +2418,10 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L13">
         <v>75</v>
@@ -2486,10 +2477,10 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -2545,10 +2536,10 @@
         <v>93.3</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L15">
         <v>95</v>
@@ -2604,10 +2595,10 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L16">
         <v>75</v>
@@ -2663,10 +2654,10 @@
         <v>93.3</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -2756,19 +2747,19 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2800,7 +2791,7 @@
         <v>28.6</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2978,7 +2969,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3010,22 +3001,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920141</v>
+        <v>21330051920147</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3033,22 +3024,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920141</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3056,16 +3047,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3079,16 +3070,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -3102,70 +3093,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920382</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920382</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920148</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="54">
   <si>
     <t>Materia</t>
   </si>
@@ -143,12 +143,12 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -167,9 +167,6 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -180,9 +177,6 @@
   </si>
   <si>
     <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
@@ -708,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -785,7 +779,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -821,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -862,7 +856,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -898,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -939,7 +933,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -975,7 +969,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1016,7 +1010,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1093,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1170,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1206,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1247,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1283,7 +1277,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1324,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1401,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1437,7 +1431,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1478,7 +1472,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1514,7 +1508,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1555,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1632,7 +1626,7 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1668,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1709,7 +1703,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1745,7 +1739,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1896,7 +1890,7 @@
         <v>90</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1955,7 +1949,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2014,7 +2008,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2073,7 +2067,7 @@
         <v>85</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2132,7 +2126,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2191,7 +2185,7 @@
         <v>95</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -2250,7 +2244,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2309,7 +2303,7 @@
         <v>90</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -2368,7 +2362,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2427,7 +2421,7 @@
         <v>75</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2486,7 +2480,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2545,7 +2539,7 @@
         <v>95</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2604,7 +2598,7 @@
         <v>75</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2663,7 +2657,7 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2834,7 +2828,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
@@ -2855,7 +2849,7 @@
         <v>7.1</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2866,7 +2860,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
@@ -2875,19 +2869,19 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2969,7 +2963,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3007,10 +3001,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -3030,10 +3024,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3047,70 +3041,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920382</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920382</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -1863,7 +1863,7 @@
         <v>50</v>
       </c>
       <c r="D4">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -1872,43 +1872,43 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>86.7</v>
+        <v>72.2</v>
       </c>
       <c r="H4">
-        <v>81.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="K4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M4">
-        <v>120</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1922,7 +1922,7 @@
         <v>93.3</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -1931,43 +1931,43 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>98.2</v>
       </c>
       <c r="I5">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1981,7 +1981,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -1990,43 +1990,43 @@
         <v>90</v>
       </c>
       <c r="G6">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H6">
-        <v>98.2</v>
+        <v>97.3</v>
       </c>
       <c r="I6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J6">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="K6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M6">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2040,7 +2040,7 @@
         <v>93.3</v>
       </c>
       <c r="D7">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -2049,43 +2049,43 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H7">
-        <v>90.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="K7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2099,7 +2099,7 @@
         <v>96.7</v>
       </c>
       <c r="D8">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -2108,43 +2108,43 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H8">
-        <v>98.2</v>
+        <v>97.3</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J8">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="K8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2158,7 +2158,7 @@
         <v>90</v>
       </c>
       <c r="D9">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -2167,43 +2167,43 @@
         <v>95</v>
       </c>
       <c r="G9">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H9">
         <v>98.2</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J9">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="K9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>95</v>
       </c>
       <c r="M9">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2217,7 +2217,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -2226,43 +2226,43 @@
         <v>95</v>
       </c>
       <c r="G10">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H10">
-        <v>92.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2276,7 +2276,7 @@
         <v>56.7</v>
       </c>
       <c r="D11">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -2285,43 +2285,43 @@
         <v>70</v>
       </c>
       <c r="G11">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="H11">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="I11">
+        <v>78.3</v>
+      </c>
+      <c r="J11">
+        <v>93.5</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>80</v>
       </c>
-      <c r="I11">
-        <v>100</v>
-      </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
-      <c r="K11">
-        <v>120</v>
-      </c>
-      <c r="L11">
-        <v>90</v>
-      </c>
       <c r="M11">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2335,7 +2335,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -2344,43 +2344,43 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>94.5</v>
+        <v>95.5</v>
       </c>
       <c r="I12">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J12">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="K12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2394,7 +2394,7 @@
         <v>36.7</v>
       </c>
       <c r="D13">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -2403,43 +2403,43 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="H13">
-        <v>81.8</v>
+        <v>77.3</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>68.3</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="K13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M13">
-        <v>120</v>
+        <v>83.3</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>68.3</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2453,7 +2453,7 @@
         <v>96.7</v>
       </c>
       <c r="D14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -2462,43 +2462,43 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H14">
-        <v>94.5</v>
+        <v>97.3</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2512,7 +2512,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -2521,43 +2521,43 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M15">
-        <v>120</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2571,7 +2571,7 @@
         <v>43.3</v>
       </c>
       <c r="D16">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -2580,43 +2580,43 @@
         <v>95</v>
       </c>
       <c r="G16">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="H16">
-        <v>90.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>71.7</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="K16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="M16">
-        <v>120</v>
+        <v>77.8</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>71.7</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2630,7 +2630,7 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -2639,43 +2639,43 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>96.40000000000001</v>
       </c>
       <c r="I17">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J17">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -1878,7 +1878,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="I4">
-        <v>75</v>
+        <v>76.3</v>
       </c>
       <c r="J4">
         <v>93.5</v>
@@ -1896,7 +1896,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="O4">
-        <v>75</v>
+        <v>76.3</v>
       </c>
       <c r="P4">
         <v>93.5</v>
@@ -1937,7 +1937,7 @@
         <v>98.2</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -1955,7 +1955,7 @@
         <v>98.2</v>
       </c>
       <c r="O5">
-        <v>95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -1996,7 +1996,7 @@
         <v>97.3</v>
       </c>
       <c r="I6">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>97.8</v>
@@ -2014,7 +2014,7 @@
         <v>97.3</v>
       </c>
       <c r="O6">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>97.8</v>
@@ -2055,7 +2055,7 @@
         <v>90</v>
       </c>
       <c r="I7">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J7">
         <v>93.5</v>
@@ -2073,7 +2073,7 @@
         <v>90</v>
       </c>
       <c r="O7">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P7">
         <v>93.5</v>
@@ -2114,7 +2114,7 @@
         <v>97.3</v>
       </c>
       <c r="I8">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>97.8</v>
@@ -2132,7 +2132,7 @@
         <v>97.3</v>
       </c>
       <c r="O8">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="P8">
         <v>97.8</v>
@@ -2173,7 +2173,7 @@
         <v>98.2</v>
       </c>
       <c r="I9">
-        <v>95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="J9">
         <v>97.8</v>
@@ -2191,7 +2191,7 @@
         <v>98.2</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P9">
         <v>97.8</v>
@@ -2232,7 +2232,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="I10">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -2250,7 +2250,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="O10">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -2291,7 +2291,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="I11">
-        <v>78.3</v>
+        <v>79.7</v>
       </c>
       <c r="J11">
         <v>93.5</v>
@@ -2309,7 +2309,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="O11">
-        <v>78.3</v>
+        <v>79.7</v>
       </c>
       <c r="P11">
         <v>93.5</v>
@@ -2350,7 +2350,7 @@
         <v>95.5</v>
       </c>
       <c r="I12">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>97.8</v>
@@ -2368,7 +2368,7 @@
         <v>95.5</v>
       </c>
       <c r="O12">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="P12">
         <v>97.8</v>
@@ -2409,7 +2409,7 @@
         <v>77.3</v>
       </c>
       <c r="I13">
-        <v>68.3</v>
+        <v>69.5</v>
       </c>
       <c r="J13">
         <v>93.5</v>
@@ -2427,7 +2427,7 @@
         <v>77.3</v>
       </c>
       <c r="O13">
-        <v>68.3</v>
+        <v>69.5</v>
       </c>
       <c r="P13">
         <v>93.5</v>
@@ -2468,7 +2468,7 @@
         <v>97.3</v>
       </c>
       <c r="I14">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -2486,7 +2486,7 @@
         <v>97.3</v>
       </c>
       <c r="O14">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -2527,7 +2527,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -2545,7 +2545,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2586,7 +2586,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="I16">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J16">
         <v>93.5</v>
@@ -2604,7 +2604,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="O16">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="P16">
         <v>93.5</v>
@@ -2645,7 +2645,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="I17">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -2663,7 +2663,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="O17">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P17">
         <v>100</v>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -146,10 +146,10 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>NC</t>
@@ -705,25 +705,25 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -782,19 +782,19 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -806,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -859,28 +859,28 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -889,7 +889,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -936,34 +936,34 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1013,19 +1013,19 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1040,10 +1040,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1090,31 +1090,31 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1167,31 +1167,31 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>8</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1244,25 +1244,25 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1321,25 +1321,25 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1398,19 +1398,19 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1428,7 +1428,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1475,25 +1475,25 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1552,25 +1552,25 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1579,7 +1579,7 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1629,25 +1629,25 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -1706,19 +1706,19 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1730,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1893,19 +1893,19 @@
         <v>86.09999999999999</v>
       </c>
       <c r="N4">
-        <v>79.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O4">
-        <v>76.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="P4">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="S4">
         <v>86.09999999999999</v>
@@ -1952,10 +1952,10 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>96.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -2011,19 +2011,19 @@
         <v>97.2</v>
       </c>
       <c r="N6">
-        <v>97.3</v>
+        <v>97.7</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="S6">
         <v>97.2</v>
@@ -2070,19 +2070,19 @@
         <v>97.2</v>
       </c>
       <c r="N7">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O7">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P7">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>92.5</v>
+        <v>88.3</v>
       </c>
       <c r="S7">
         <v>97.2</v>
@@ -2129,13 +2129,13 @@
         <v>97.2</v>
       </c>
       <c r="N8">
-        <v>97.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -2188,19 +2188,19 @@
         <v>97.2</v>
       </c>
       <c r="N9">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="O9">
-        <v>96.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P9">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="S9">
         <v>97.2</v>
@@ -2247,19 +2247,19 @@
         <v>97.2</v>
       </c>
       <c r="N10">
-        <v>90.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="S10">
         <v>97.2</v>
@@ -2306,19 +2306,19 @@
         <v>88.90000000000001</v>
       </c>
       <c r="N11">
-        <v>73.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O11">
-        <v>79.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P11">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>80</v>
+        <v>81.7</v>
       </c>
       <c r="S11">
         <v>88.90000000000001</v>
@@ -2365,19 +2365,19 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -2424,19 +2424,19 @@
         <v>83.3</v>
       </c>
       <c r="N13">
-        <v>77.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="O13">
-        <v>69.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P13">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="S13">
         <v>83.3</v>
@@ -2483,7 +2483,7 @@
         <v>97.2</v>
       </c>
       <c r="N14">
-        <v>97.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -2542,10 +2542,10 @@
         <v>94.40000000000001</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O15">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2554,7 +2554,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="S15">
         <v>94.40000000000001</v>
@@ -2601,19 +2601,19 @@
         <v>77.8</v>
       </c>
       <c r="N16">
-        <v>79.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O16">
-        <v>72.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="P16">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="S16">
         <v>77.8</v>
@@ -2660,19 +2660,19 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>96.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O17">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -2753,7 +2753,7 @@
         <v>28.6</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>28.6</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
@@ -2881,7 +2881,7 @@
         <v>7.1</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>43</v>
@@ -2901,19 +2901,19 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/4ASV - Estadisticos 20222.xlsx
+++ b/grupos/4ASV - Estadisticos 20222.xlsx
@@ -720,7 +720,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -738,7 +738,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -797,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -874,7 +874,7 @@
         <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1028,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1105,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1123,7 +1123,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1182,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1200,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1259,7 +1259,7 @@
         <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1277,7 +1277,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1336,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1413,7 +1413,7 @@
         <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1431,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1490,7 +1490,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1508,7 +1508,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1567,7 +1567,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1585,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1644,7 +1644,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1721,7 +1721,7 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1739,7 +1739,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1908,7 +1908,7 @@
         <v>91.7</v>
       </c>
       <c r="S4">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2026,7 +2026,7 @@
         <v>96.7</v>
       </c>
       <c r="S6">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2085,7 +2085,7 @@
         <v>88.3</v>
       </c>
       <c r="S7">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2144,7 +2144,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2203,7 +2203,7 @@
         <v>93.3</v>
       </c>
       <c r="S9">
-        <v>97.2</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2262,7 +2262,7 @@
         <v>98.3</v>
       </c>
       <c r="S10">
-        <v>97.2</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2321,7 +2321,7 @@
         <v>81.7</v>
       </c>
       <c r="S11">
-        <v>88.90000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2498,7 +2498,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>97.2</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2557,7 +2557,7 @@
         <v>95</v>
       </c>
       <c r="S15">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2616,7 +2616,7 @@
         <v>88.3</v>
       </c>
       <c r="S16">
-        <v>77.8</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2837,19 +2837,19 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>92.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G5" s="2">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
